--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -15824,12 +15824,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15854,12 +15854,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N102" t="n">
@@ -15902,42 +15902,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15969,12 +15969,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -16047,40 +16047,185 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW103" t="inlineStr">
+      <c r="AW104" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
+      <c r="AX104" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY103" t="inlineStr">
+      <c r="AY104" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
+      <c r="AZ104" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA103" t="inlineStr">
+      <c r="BA104" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB103" t="inlineStr">
+      <c r="BB104" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC103" t="inlineStr">
+      <c r="BC104" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -16202,7 +16347,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -16212,7 +16357,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -11643,12 +11643,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11682,81 +11682,92 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11783,17 +11794,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11827,81 +11838,170 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>West Nile Virus Illness</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary West Nile virus surveillance notifications combining confirmed and probable cases across neurologic, non-neurologic and asymptomatic infection classifications.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11933,12 +12033,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11963,7 +12063,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -12011,42 +12111,42 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12078,12 +12178,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -12108,7 +12208,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -12117,13 +12217,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -12156,42 +12256,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12253,7 +12353,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -12368,12 +12468,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12398,7 +12498,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -12407,13 +12507,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -12446,42 +12546,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12513,12 +12613,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12543,7 +12643,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -12552,13 +12652,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -12591,42 +12691,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12788,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -12833,7 +12933,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -12842,13 +12942,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R81" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -12978,7 +13078,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -13093,12 +13193,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13123,22 +13223,22 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -13171,42 +13271,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13238,12 +13338,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -13268,12 +13368,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13282,9 +13382,12 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13313,42 +13416,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13380,12 +13483,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13424,9 +13527,12 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13460,12 +13566,12 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -13480,12 +13586,12 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
@@ -13522,12 +13628,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13602,7 +13708,7 @@
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -13622,7 +13728,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -13664,12 +13770,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13744,7 +13850,7 @@
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -13764,7 +13870,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -13806,12 +13912,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13886,7 +13992,7 @@
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
@@ -13906,7 +14012,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -13948,12 +14054,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -14028,7 +14134,7 @@
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
@@ -14048,7 +14154,7 @@
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
@@ -14090,12 +14196,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -14170,7 +14276,7 @@
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
@@ -14190,7 +14296,7 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
@@ -14232,12 +14338,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14312,7 +14418,7 @@
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
@@ -14332,7 +14438,7 @@
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
@@ -14374,12 +14480,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14418,12 +14524,9 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14452,42 +14555,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14519,12 +14622,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14558,17 +14661,14 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -14597,42 +14697,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14664,12 +14764,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14694,7 +14794,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -14742,42 +14842,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14939,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -14848,13 +14948,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -14984,7 +15084,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -15129,7 +15229,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -15138,13 +15238,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O97" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R97" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -15274,7 +15374,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -15419,7 +15519,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -15428,13 +15528,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O99" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R99" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -15564,7 +15664,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -15709,7 +15809,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -15718,13 +15818,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O101" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R101" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -15854,7 +15954,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -15969,12 +16069,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15999,22 +16099,22 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -16047,42 +16147,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16114,12 +16214,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -16144,12 +16244,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -16192,40 +16292,330 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW104" t="inlineStr">
+      <c r="AW106" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
+      <c r="AX106" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY104" t="inlineStr">
+      <c r="AY106" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
+      <c r="AZ106" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA104" t="inlineStr">
+      <c r="BA106" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB104" t="inlineStr">
+      <c r="BB106" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC104" t="inlineStr">
+      <c r="BC106" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -16347,7 +16737,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -16357,7 +16747,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
@@ -16377,7 +16767,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -16409,7 +16799,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -16621,6 +16621,151 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16654,7 +16799,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -16747,7 +16892,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -14764,12 +14764,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14842,42 +14842,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14909,12 +14909,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14948,13 +14948,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -14987,42 +14987,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15054,12 +15054,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -15093,13 +15093,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -15132,42 +15132,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -15238,13 +15238,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.001432519066384693</v>
+        <v>0</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -15277,42 +15277,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -15383,13 +15383,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -15422,42 +15422,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15489,12 +15489,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -15528,13 +15528,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.00200552669293857</v>
+        <v>0</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -15567,42 +15567,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15634,12 +15634,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -15673,13 +15673,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -15712,42 +15712,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15779,12 +15779,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -15818,13 +15818,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0.002578534319492447</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -15857,42 +15857,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15924,12 +15924,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -15963,13 +15963,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -16002,42 +16002,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16069,12 +16069,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.001719022879661631</v>
+        <v>0</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -16147,42 +16147,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16214,12 +16214,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -16253,13 +16253,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -16292,42 +16292,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16359,12 +16359,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -16389,12 +16389,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -16437,42 +16437,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16504,12 +16504,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16582,42 +16582,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16649,12 +16649,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -16727,42 +16727,477 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW107" t="inlineStr">
+      <c r="AW108" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
+      <c r="AX108" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY107" t="inlineStr">
+      <c r="AY108" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
+      <c r="AZ108" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA107" t="inlineStr">
+      <c r="BA108" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB107" t="inlineStr">
+      <c r="BB108" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC107" t="inlineStr">
+      <c r="BC108" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>11</v>
+      </c>
+      <c r="O110" t="n">
+        <v>11</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.003151541946046324</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16799,7 +17234,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -16882,7 +17317,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -16892,7 +17327,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -16944,7 +17379,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -17201,6 +17201,441 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>5</v>
+      </c>
+      <c r="O112" t="n">
+        <v>5</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17234,7 +17669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -17317,7 +17752,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -17327,7 +17762,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11">
@@ -17379,7 +17814,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -15054,12 +15054,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -15093,81 +15093,100 @@
         </is>
       </c>
       <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
         <v>2</v>
       </c>
-      <c r="O96" t="n">
-        <v>2</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP96" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
-      <c r="AT96" t="n">
-        <v>0</v>
-      </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -15194,17 +15213,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15229,7 +15248,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -15243,76 +15262,170 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Vestnilfeber</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -15374,7 +15487,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -15383,13 +15496,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O98" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -15519,7 +15632,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -15664,7 +15777,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -15673,13 +15786,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O100" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R100" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -15809,7 +15922,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -15954,7 +16067,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -15963,13 +16076,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O102" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R102" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -16099,7 +16212,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -16244,7 +16357,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -16253,13 +16366,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O104" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R104" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -16389,7 +16502,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -16504,12 +16617,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16534,22 +16647,22 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -16582,42 +16695,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16649,12 +16762,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16679,12 +16792,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N107" t="n">
@@ -16727,42 +16840,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16794,12 +16907,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16824,7 +16937,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -16872,42 +16985,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16939,12 +17052,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -16969,7 +17082,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -17017,42 +17130,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17084,12 +17197,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -17114,7 +17227,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -17123,81 +17236,100 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>0.003151541946046324</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17224,17 +17356,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -17259,7 +17391,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -17268,81 +17400,175 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Vestnilfeber</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17374,12 +17600,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17404,7 +17630,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -17413,13 +17639,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0.001432519066384693</v>
+        <v>0</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -17452,42 +17678,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17519,12 +17745,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17549,12 +17775,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -17597,40 +17823,620 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>11</v>
+      </c>
+      <c r="O114" t="n">
+        <v>11</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.003151541946046324</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>5</v>
+      </c>
+      <c r="O116" t="n">
+        <v>5</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW113" t="inlineStr">
+      <c r="AW117" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
+      <c r="AX117" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY113" t="inlineStr">
+      <c r="AY117" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
+      <c r="AZ117" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA113" t="inlineStr">
+      <c r="BA117" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB113" t="inlineStr">
+      <c r="BB117" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC113" t="inlineStr">
+      <c r="BC117" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -17752,7 +18558,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -17762,7 +18568,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -17782,7 +18588,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -17792,7 +18598,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -17814,7 +18620,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2471,6 +2516,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2616,6 +2666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3356,6 +3411,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3501,6 +3561,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3646,6 +3711,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3791,6 +3861,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3936,6 +4011,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4081,6 +4161,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4226,6 +4311,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4371,6 +4461,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4516,6 +4611,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5051,6 +5151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5196,6 +5301,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5936,6 +6046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6081,6 +6196,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6226,6 +6346,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6371,6 +6496,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6516,6 +6646,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6661,6 +6796,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6806,6 +6946,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6951,6 +7096,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7096,6 +7246,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7631,6 +7786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7776,6 +7936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8513,6 +8678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8658,6 +8828,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8803,6 +8978,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8948,6 +9128,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9093,6 +9278,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9238,6 +9428,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9383,6 +9578,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9528,6 +9728,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9673,6 +9878,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10208,6 +10418,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10353,6 +10568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11090,6 +11310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11235,6 +11460,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11380,6 +11610,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11525,6 +11760,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11670,6 +11910,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11815,6 +12060,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11960,6 +12210,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12105,6 +12360,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12250,6 +12510,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12785,6 +13050,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12930,6 +13200,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13815,6 +14090,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13960,6 +14240,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14381,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14241,6 +14531,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14386,6 +14681,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14531,6 +14831,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14676,6 +14981,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14821,6 +15131,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14966,6 +15281,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15501,6 +15821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15646,6 +15971,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16371,6 +16701,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16516,6 +16851,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16661,6 +17001,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16806,6 +17151,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16951,6 +17301,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17096,6 +17451,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17241,6 +17601,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17386,6 +17751,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17531,6 +17901,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17663,10 +18038,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -17819,10 +18194,10 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -18066,6 +18441,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18211,6 +18591,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19516,6 +19901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19661,6 +20051,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19806,6 +20201,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19951,6 +20351,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20096,6 +20501,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20241,6 +20651,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20386,6 +20801,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20531,6 +20951,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20676,6 +21101,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20769,12 +21199,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -20808,81 +21238,92 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20909,17 +21350,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -20953,81 +21394,170 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>58</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>West Nile Virus Illness</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary West Nile virus surveillance notifications combining confirmed and probable cases across neurologic, non-neurologic and asymptomatic infection classifications.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21059,12 +21589,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -21111,11 +21641,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21123,75 +21648,66 @@
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21218,17 +21734,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -21267,34 +21783,12 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Vestnilfeber</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -21302,135 +21796,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
-      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21462,12 +21889,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -21501,81 +21928,100 @@
         </is>
       </c>
       <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
         <v>2</v>
       </c>
-      <c r="O139" t="n">
-        <v>2</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP139" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
-      <c r="AT139" t="n">
-        <v>0</v>
-      </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21602,17 +22048,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -21637,7 +22083,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -21651,76 +22097,170 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Vestnilfeber</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; revised</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21782,7 +22322,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -21791,13 +22331,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R141" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -21927,7 +22467,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -22072,7 +22612,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -22081,13 +22621,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O143" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R143" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -22217,7 +22757,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -22362,7 +22902,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -22371,13 +22911,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O145" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R145" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -22507,7 +23047,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -22652,7 +23192,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -22661,13 +23201,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O147" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R147" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -22797,7 +23337,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -22912,12 +23452,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -22942,22 +23482,22 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -22990,42 +23530,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23057,12 +23597,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -23087,12 +23627,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N150" t="n">
@@ -23106,7 +23646,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -23135,42 +23675,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23202,12 +23742,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -23251,7 +23791,12 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -23285,12 +23830,12 @@
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -23305,12 +23850,12 @@
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
@@ -23347,12 +23892,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -23397,6 +23942,11 @@
       <c r="S152" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -23430,7 +23980,7 @@
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
@@ -23450,7 +24000,7 @@
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
@@ -23492,12 +24042,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -23542,6 +24092,11 @@
       <c r="S153" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -23575,7 +24130,7 @@
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
@@ -23595,7 +24150,7 @@
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
@@ -23637,12 +24192,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -23687,6 +24242,11 @@
       <c r="S154" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -23720,7 +24280,7 @@
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
@@ -23740,7 +24300,7 @@
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
@@ -23782,12 +24342,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -23832,6 +24392,11 @@
       <c r="S155" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -23865,7 +24430,7 @@
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
@@ -23885,7 +24450,7 @@
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
@@ -23927,12 +24492,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -23977,6 +24542,11 @@
       <c r="S156" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -24010,7 +24580,7 @@
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -24030,7 +24600,7 @@
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
@@ -24072,12 +24642,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -24122,6 +24692,11 @@
       <c r="S157" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -24155,7 +24730,7 @@
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
@@ -24175,7 +24750,7 @@
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
@@ -24217,12 +24792,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -24266,7 +24841,12 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -24295,42 +24875,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24362,12 +24942,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -24401,22 +24981,17 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -24426,75 +25001,66 @@
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24521,17 +25087,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -24565,39 +25131,17 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>1</v>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Vestnilfeber</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -24605,135 +25149,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>1</v>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_512_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24765,12 +25242,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -24795,7 +25272,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -24804,81 +25281,100 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24905,17 +25401,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -24940,7 +25436,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -24949,81 +25445,175 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Vestnilfeber</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; revised</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25055,12 +25645,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -25085,7 +25675,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -25094,13 +25684,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>0.003151541946046324</v>
+        <v>0</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -25133,42 +25723,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25230,7 +25820,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -25375,7 +25965,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -25384,13 +25974,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O165" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R165" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.003151541946046324</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -25520,7 +26110,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -25635,12 +26225,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -25665,22 +26255,22 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -25713,42 +26303,885 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW167" t="inlineStr">
+      <c r="AW169" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX167" t="inlineStr">
+      <c r="AX169" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY167" t="inlineStr">
+      <c r="AY169" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ167" t="inlineStr">
+      <c r="AZ169" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA167" t="inlineStr">
+      <c r="BA169" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB167" t="inlineStr">
+      <c r="BB169" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC167" t="inlineStr">
+      <c r="BC169" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Vestnilfeber</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; revised</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_512_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>5</v>
+      </c>
+      <c r="O172" t="n">
+        <v>5</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25785,7 +27218,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -25868,7 +27301,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -25878,7 +27311,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -25898,7 +27331,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -25930,7 +27363,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -27185,6 +27185,151 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27218,7 +27363,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -27301,7 +27446,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
@@ -27311,7 +27456,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -18886,6 +18886,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19321,6 +19326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19611,6 +19621,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22344,6 +22359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22634,6 +22654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22924,6 +22949,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23214,6 +23244,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23504,6 +23539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25987,6 +26027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26277,6 +26322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27120,6 +27170,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27327,6 +27382,156 @@
       <c r="BC173" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>8</v>
+      </c>
+      <c r="O174" t="n">
+        <v>8</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.002292030506215508</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27568,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -27446,7 +27651,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -27456,7 +27661,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -27508,7 +27713,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
